--- a/data/firms/futureselite.xlsx
+++ b/data/firms/futureselite.xlsx
@@ -805,7 +805,7 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>L'emplacement disparait de la page. Rien n'est invente pour le combler.</t>
+          <t>Carte d'identite et bande : la case affiche « — ». Ailleurs, l'emplacement disparait. Rien n'est invente.</t>
         </is>
       </c>
     </row>
@@ -872,7 +872,7 @@
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>« Who we recommend [Firm] for » : verdict, bons profils, « Consider another firm if… »</t>
+          <t>« Who we recommend [Firm] for » : verdict, bons profils, « Consider another firm if… » · « Strengths and things to know » : points forts et limites</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>Si sa portee n'est pas confirmee, le prix s'affiche avec « ≈ » et la mention « Estimated price — verify at checkout ».</t>
+          <t>Si sa portee n'est pas confirmee, le prix remise s'affiche avec « ≈ » devant.</t>
         </is>
       </c>
     </row>
@@ -1067,7 +1067,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1268,6 +1268,18 @@
       <c r="E5" s="11" t="inlineStr">
         <is>
           <t>Static</t>
+        </is>
+      </c>
+      <c r="I5" s="11" t="inlineStr">
+        <is>
+          <t>point_fort</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="I6" s="11" t="inlineStr">
+        <is>
+          <t>limite</t>
         </is>
       </c>
     </row>
@@ -1438,7 +1450,7 @@
       </c>
       <c r="D7" s="18" t="inlineStr">
         <is>
-          <t>« Founded ». Vide : la case disparait.</t>
+          <t>« Founded ». Vide : « — ».</t>
         </is>
       </c>
     </row>
@@ -1478,7 +1490,7 @@
       </c>
       <c r="D9" s="18" t="inlineStr">
         <is>
-          <t>« CEO / Founder ». Vide : la case disparait.</t>
+          <t>« CEO / Founder ». Vide : « — ».</t>
         </is>
       </c>
     </row>
@@ -1558,7 +1570,7 @@
       </c>
       <c r="D13" s="18" t="inlineStr">
         <is>
-          <t>« Trading profile » : « Leverage 1:X ». Vide : l'etiquette disparait.</t>
+          <t>« Trading profile » : « Leverage 1:X ». Vide : « Leverage — ».</t>
         </is>
       </c>
     </row>
@@ -2174,7 +2186,11 @@
       <c r="E5" s="27" t="n">
         <v>293</v>
       </c>
-      <c r="F5" s="16" t="n"/>
+      <c r="F5" s="16" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
       <c r="G5" s="22">
         <f>IF(A5="","",SUMPRODUCT((Phases!$A$3:$A$900=A5)*(Phases!$B$3:$B$900=B5)*(Phases!$C$3:$C$900=C5)))</f>
         <v/>
@@ -5315,7 +5331,11 @@
           <t>Trailing Equity</t>
         </is>
       </c>
-      <c r="H12" s="26" t="n"/>
+      <c r="H12" s="26" t="inlineStr">
+        <is>
+          <t>aucune</t>
+        </is>
+      </c>
       <c r="I12" s="19" t="n">
         <v>1</v>
       </c>
@@ -5405,7 +5425,11 @@
           <t>Trailing Equity</t>
         </is>
       </c>
-      <c r="H14" s="26" t="n"/>
+      <c r="H14" s="26" t="inlineStr">
+        <is>
+          <t>aucune</t>
+        </is>
+      </c>
       <c r="I14" s="19" t="n">
         <v>1</v>
       </c>
@@ -5495,7 +5519,11 @@
           <t>Trailing Equity</t>
         </is>
       </c>
-      <c r="H16" s="26" t="n"/>
+      <c r="H16" s="26" t="inlineStr">
+        <is>
+          <t>aucune</t>
+        </is>
+      </c>
       <c r="I16" s="19" t="n">
         <v>1</v>
       </c>
@@ -5585,7 +5613,11 @@
           <t>Trailing Equity</t>
         </is>
       </c>
-      <c r="H18" s="26" t="n"/>
+      <c r="H18" s="26" t="inlineStr">
+        <is>
+          <t>aucune</t>
+        </is>
+      </c>
       <c r="I18" s="19" t="n">
         <v>1</v>
       </c>
@@ -5973,7 +6005,11 @@
           <t>End of Day</t>
         </is>
       </c>
-      <c r="H27" s="26" t="n"/>
+      <c r="H27" s="26" t="inlineStr">
+        <is>
+          <t>aucune</t>
+        </is>
+      </c>
       <c r="I27" s="19" t="n">
         <v>10</v>
       </c>
@@ -6015,7 +6051,11 @@
           <t>End of Day</t>
         </is>
       </c>
-      <c r="H28" s="26" t="n"/>
+      <c r="H28" s="26" t="inlineStr">
+        <is>
+          <t>aucune</t>
+        </is>
+      </c>
       <c r="I28" s="19" t="n">
         <v>10</v>
       </c>
@@ -6057,7 +6097,11 @@
           <t>End of Day</t>
         </is>
       </c>
-      <c r="H29" s="26" t="n"/>
+      <c r="H29" s="26" t="inlineStr">
+        <is>
+          <t>aucune</t>
+        </is>
+      </c>
       <c r="I29" s="19" t="n">
         <v>10</v>
       </c>
@@ -12935,7 +12979,7 @@
       </c>
       <c r="D4" s="18" t="inlineStr">
         <is>
-          <t>non_confirmee → prix avec « ≈ » et « Estimated price — verify at checkout ».</t>
+          <t>non_confirmee → prix remise affiche avec « ≈ ». Sert aussi la reponse FAQ sur le code.</t>
         </is>
       </c>
     </row>
@@ -12975,7 +13019,7 @@
       </c>
       <c r="D6" s="18" t="inlineStr">
         <is>
-          <t>La mention sous le code et la reponse FAQ « Does the promotional code apply to every account? ». Slugs separes par des virgules.</t>
+          <t>Le prix remise ne s'affiche que sur ces programmes, et la reponse FAQ « Does the promotional code apply to every account? ». Slugs separes par des virgules.</t>
         </is>
       </c>
     </row>
@@ -13011,7 +13055,7 @@
       </c>
       <c r="D8" s="18" t="inlineStr">
         <is>
-          <t>La mention sous le code. Vide : « no published expiry ».</t>
+          <t>Non affiche sur la page pour l'instant.</t>
         </is>
       </c>
     </row>
@@ -13146,7 +13190,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C35"/>
+  <dimension ref="A1:C37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -13174,7 +13218,7 @@
     <row r="2" ht="58" customHeight="1">
       <c r="A2" s="21" t="inlineStr">
         <is>
-          <t>verdict = « Our verdict » · pour_qui = liste ✓ · pas_pour = « Consider another firm if… »</t>
+          <t>verdict = « Our verdict » · pour_qui = liste ✓ · pas_pour = « Consider another firm if… » · point_fort = « Strengths » · limite = « Things to know »</t>
         </is>
       </c>
       <c r="B2" s="21" t="inlineStr">
@@ -13339,59 +13383,169 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="16" t="n"/>
-      <c r="B13" s="19" t="n"/>
-      <c r="C13" s="16" t="n"/>
+      <c r="A13" s="16" t="inlineStr">
+        <is>
+          <t>point_fort</t>
+        </is>
+      </c>
+      <c r="B13" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" s="16" t="inlineStr">
+        <is>
+          <t>90% profit split on Elite, Nitro and Prime; 80% on Instant</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="16" t="n"/>
-      <c r="B14" s="19" t="n"/>
-      <c r="C14" s="16" t="n"/>
+      <c r="A14" s="16" t="inlineStr">
+        <is>
+          <t>point_fort</t>
+        </is>
+      </c>
+      <c r="B14" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="C14" s="16" t="inlineStr">
+        <is>
+          <t>Drawdown type differs by program and phase — see the rules table</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="16" t="n"/>
-      <c r="B15" s="19" t="n"/>
-      <c r="C15" s="16" t="n"/>
+      <c r="A15" s="16" t="inlineStr">
+        <is>
+          <t>point_fort</t>
+        </is>
+      </c>
+      <c r="B15" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="C15" s="16" t="inlineStr">
+        <is>
+          <t>No daily loss limit on Elite, Nitro and Instant — Prime has one in both phases</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="16" t="n"/>
-      <c r="B16" s="19" t="n"/>
-      <c r="C16" s="16" t="n"/>
+      <c r="A16" s="16" t="inlineStr">
+        <is>
+          <t>point_fort</t>
+        </is>
+      </c>
+      <c r="B16" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="C16" s="16" t="inlineStr">
+        <is>
+          <t>No funded consistency rule on Elite and Nitro</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="16" t="n"/>
-      <c r="B17" s="19" t="n"/>
-      <c r="C17" s="16" t="n"/>
+      <c r="A17" s="16" t="inlineStr">
+        <is>
+          <t>point_fort</t>
+        </is>
+      </c>
+      <c r="B17" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="C17" s="16" t="inlineStr">
+        <is>
+          <t>No activation fee to unlock the funded account</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="16" t="n"/>
-      <c r="B18" s="19" t="n"/>
-      <c r="C18" s="16" t="n"/>
+      <c r="A18" s="16" t="inlineStr">
+        <is>
+          <t>point_fort</t>
+        </is>
+      </c>
+      <c r="B18" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="C18" s="16" t="inlineStr">
+        <is>
+          <t>Payouts available every day once funded</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="16" t="n"/>
-      <c r="B19" s="19" t="n"/>
-      <c r="C19" s="16" t="n"/>
+      <c r="A19" s="16" t="inlineStr">
+        <is>
+          <t>point_fort</t>
+        </is>
+      </c>
+      <c r="B19" s="19" t="n">
+        <v>7</v>
+      </c>
+      <c r="C19" s="16" t="inlineStr">
+        <is>
+          <t>Bundle discounts: the fifth account is free</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="16" t="n"/>
-      <c r="B20" s="19" t="n"/>
-      <c r="C20" s="16" t="n"/>
+      <c r="A20" s="16" t="inlineStr">
+        <is>
+          <t>limite</t>
+        </is>
+      </c>
+      <c r="B20" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" s="16" t="inlineStr">
+        <is>
+          <t>No financial regulator licence</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="16" t="n"/>
-      <c r="B21" s="19" t="n"/>
-      <c r="C21" s="16" t="n"/>
+      <c r="A21" s="16" t="inlineStr">
+        <is>
+          <t>limite</t>
+        </is>
+      </c>
+      <c r="B21" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="C21" s="16" t="inlineStr">
+        <is>
+          <t>Demo accounts, hypothetical performance</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="16" t="n"/>
-      <c r="B22" s="19" t="n"/>
-      <c r="C22" s="16" t="n"/>
+      <c r="A22" s="16" t="inlineStr">
+        <is>
+          <t>limite</t>
+        </is>
+      </c>
+      <c r="B22" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="C22" s="16" t="inlineStr">
+        <is>
+          <t>Minimum days differ by program; Elite needs 6 profitable days above a size-based threshold before a payout</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" s="16" t="n"/>
-      <c r="B23" s="19" t="n"/>
-      <c r="C23" s="16" t="n"/>
+      <c r="A23" s="16" t="inlineStr">
+        <is>
+          <t>limite</t>
+        </is>
+      </c>
+      <c r="B23" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="C23" s="16" t="inlineStr">
+        <is>
+          <t>Per-request payout cap, from $1,000 to $3,000 by account size</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="16" t="n"/>
@@ -13453,10 +13607,20 @@
       <c r="B35" s="19" t="n"/>
       <c r="C35" s="16" t="n"/>
     </row>
+    <row r="36">
+      <c r="A36" s="16" t="n"/>
+      <c r="B36" s="19" t="n"/>
+      <c r="C36" s="16" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="16" t="n"/>
+      <c r="B37" s="19" t="n"/>
+      <c r="C37" s="16" t="n"/>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="A3:A35" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valeur hors liste" error="Choisis une valeur dans la liste deroulante." type="list">
-      <formula1>=Listes!$I$2:$I$4</formula1>
+    <dataValidation sqref="A3:A37" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valeur hors liste" error="Choisis une valeur dans la liste deroulante." type="list">
+      <formula1>=Listes!$I$2:$I$6</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -13509,7 +13673,7 @@
       </c>
       <c r="C2" s="21" t="inlineStr">
         <is>
-          <t>Verifiee, sans rien supposer. Vide : la question disparait.</t>
+          <t>Vide : la page recompose la reponse depuis les autres onglets (programmes, prix, partage, retraits, offre).</t>
         </is>
       </c>
     </row>

--- a/data/firms/futureselite.xlsx
+++ b/data/firms/futureselite.xlsx
@@ -836,7 +836,7 @@
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>« Build your account » : les 4 selecteurs, le prix, les 4 metriques · « Rules by phase » : le tableau Evaluation / Funded</t>
+          <t>« Account configurator » : les etapes, le prix, la selection · « Rules by phase » : le tableau Evaluation / Funded</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="D4" s="18" t="inlineStr">
         <is>
-          <t>Le carre « FIRM LOGO ». Une image qui existe vraiment. Vide : initiale du nom.</t>
+          <t>Le logo, cliquable : il ouvre le site de la firme par ton lien d'affiliation, code promo compris. Vide : initiale du nom.</t>
         </is>
       </c>
     </row>
@@ -1410,7 +1410,7 @@
       </c>
       <c r="D5" s="18" t="inlineStr">
         <is>
-          <t>L'etiquette « [Market] prop firm » et « Firm type » (CFD / Futures / Both, deduit d'ici). futures, cfd — separes par une virgule si plusieurs.</t>
+          <t>« Firm type » (deduit d'ici) et le choix du marche dans le configurateur. futures, cfd — separes par une virgule si plusieurs.</t>
         </is>
       </c>
     </row>
@@ -1422,17 +1422,19 @@
       </c>
       <c r="B6" s="16" t="inlineStr">
         <is>
+          <t>FuturesElite sells simulated futures accounts across four programs. Elite and Prime are evaluation routes with a one-time fee and no deadline to pass. Nitro and Instant shorten or remove the evaluation entirely, Instant funding you from purchase with no objective to reach. Elite, Nitro and Prime settle at a 90% profit split; Instant pays 80%. Payouts can be requested daily once an account is funded, subject to each program’s own minimum days.
+It suits futures traders who already have a method and want to choose the rule set that fits it, rather than accept one. Loss limits are dollar amounts rather than percentages, drawdown is calculated at the end of the day on the evaluation programs, and six platforms are selectable at purchase, including Tradovate, NinjaTrader and Quantower.
+The caveat matters more than the pricing. Quantum SRL holds no financial regulator licence, and every account is simulated: performance is hypothetical throughout. The live trading program exists but is a risk-team decision, not an entitlement earned at a fixed number of payouts.</t>
+        </is>
+      </c>
+      <c r="C6" s="17" t="inlineStr">
+        <is>
           <t>FuturesElite sells simulated futures accounts across four programs. Elite and Prime are evaluation routes with a one-time fee and no deadline to pass.</t>
         </is>
       </c>
-      <c r="C6" s="17" t="inlineStr">
-        <is>
-          <t>FuturesElite sells simulated futures accounts across four programs. Elite and Prime are evaluation routes with a one-time fee and no deadline to pass.</t>
-        </is>
-      </c>
       <c r="D6" s="18" t="inlineStr">
         <is>
-          <t>Le paragraphe sous le nom. Factuel, 2 a 3 lignes maximum.</t>
+          <t>Le texte sous le nom. Factuel et developpe : separe les paragraphes par une ligne vide (Alt+Entree deux fois).</t>
         </is>
       </c>
     </row>
@@ -1442,11 +1444,11 @@
           <t>annee_creation</t>
         </is>
       </c>
-      <c r="B7" s="19" t="n"/>
-      <c r="C7" s="20" t="inlineStr">
-        <is>
-          <t>(vide — absente du releve)</t>
-        </is>
+      <c r="B7" s="19" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C7" s="20" t="n">
+        <v>2024</v>
       </c>
       <c r="D7" s="18" t="inlineStr">
         <is>
@@ -1482,10 +1484,14 @@
           <t>ceo_fondateur</t>
         </is>
       </c>
-      <c r="B9" s="16" t="n"/>
+      <c r="B9" s="16" t="inlineStr">
+        <is>
+          <t>Christian Habibi</t>
+        </is>
+      </c>
       <c r="C9" s="17" t="inlineStr">
         <is>
-          <t>(vide — absent du releve)</t>
+          <t>Christian Habibi</t>
         </is>
       </c>
       <c r="D9" s="18" t="inlineStr">
@@ -1502,12 +1508,12 @@
       </c>
       <c r="B10" s="16" t="inlineStr">
         <is>
-          <t>Futures</t>
+          <t>Futures, Forex, Metals, Indices, Energy, Crypto, Bonds, Agricultural Products</t>
         </is>
       </c>
       <c r="C10" s="17" t="inlineStr">
         <is>
-          <t>Futures</t>
+          <t>Futures, Forex, Metals, Indices, Energy, Crypto, Bonds, Agricultural Products</t>
         </is>
       </c>
       <c r="D10" s="18" t="inlineStr">
@@ -1544,10 +1550,14 @@
           <t>moyens_paiement</t>
         </is>
       </c>
-      <c r="B12" s="16" t="n"/>
+      <c r="B12" s="16" t="inlineStr">
+        <is>
+          <t>Credit/Debit Card, Crypto</t>
+        </is>
+      </c>
       <c r="C12" s="17" t="inlineStr">
         <is>
-          <t>(vide — non documentes publiquement)</t>
+          <t>Credit/Debit Card, Crypto</t>
         </is>
       </c>
       <c r="D12" s="18" t="inlineStr">
@@ -1605,7 +1615,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1613,7 +1623,8 @@
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="32" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -1644,6 +1655,11 @@
       </c>
       <c r="F1" s="14" t="inlineStr">
         <is>
+          <t>accroche</t>
+        </is>
+      </c>
+      <c r="G1" s="14" t="inlineStr">
+        <is>
           <t>nb_plans  (auto)</t>
         </is>
       </c>
@@ -1656,12 +1672,12 @@
       </c>
       <c r="B2" s="21" t="inlineStr">
         <is>
-          <t>Bouton « 2. Choose a programme ».</t>
+          <t>Carte « How do you want to be funded? ».</t>
         </is>
       </c>
       <c r="C2" s="21" t="inlineStr">
         <is>
-          <t>Bouton « 1. Choose a market ». Masque s'il n'y en a qu'un.</t>
+          <t>Carte « Choose your market ». Masquee s'il n'y en a qu'un.</t>
         </is>
       </c>
       <c r="D2" s="21" t="inlineStr">
@@ -1675,6 +1691,11 @@
         </is>
       </c>
       <c r="F2" s="21" t="inlineStr">
+        <is>
+          <t>Petite phrase au-dessus du nom dans « How do you want to be funded? ». Vide : le type (Evaluation / No evaluation).</t>
+        </is>
+      </c>
+      <c r="G2" s="21" t="inlineStr">
         <is>
           <t>Plans rattaches.</t>
         </is>
@@ -1706,7 +1727,8 @@
           <t>active</t>
         </is>
       </c>
-      <c r="F3" s="22">
+      <c r="F3" s="16" t="n"/>
+      <c r="G3" s="22">
         <f>IF(A3="","",COUNTIF(Plans!$A$3:$A$300,A3))</f>
         <v/>
       </c>
@@ -1737,7 +1759,8 @@
           <t>active</t>
         </is>
       </c>
-      <c r="F4" s="22">
+      <c r="F4" s="16" t="n"/>
+      <c r="G4" s="22">
         <f>IF(A4="","",COUNTIF(Plans!$A$3:$A$300,A4))</f>
         <v/>
       </c>
@@ -1768,7 +1791,8 @@
           <t>active</t>
         </is>
       </c>
-      <c r="F5" s="22">
+      <c r="F5" s="16" t="n"/>
+      <c r="G5" s="22">
         <f>IF(A5="","",COUNTIF(Plans!$A$3:$A$300,A5))</f>
         <v/>
       </c>
@@ -1799,7 +1823,8 @@
           <t>active</t>
         </is>
       </c>
-      <c r="F6" s="22">
+      <c r="F6" s="16" t="n"/>
+      <c r="G6" s="22">
         <f>IF(A6="","",COUNTIF(Plans!$A$3:$A$300,A6))</f>
         <v/>
       </c>
@@ -1810,7 +1835,8 @@
       <c r="C7" s="16" t="n"/>
       <c r="D7" s="16" t="n"/>
       <c r="E7" s="16" t="n"/>
-      <c r="F7" s="22">
+      <c r="F7" s="16" t="n"/>
+      <c r="G7" s="22">
         <f>IF(A7="","",COUNTIF(Plans!$A$3:$A$300,A7))</f>
         <v/>
       </c>
@@ -1821,7 +1847,8 @@
       <c r="C8" s="16" t="n"/>
       <c r="D8" s="16" t="n"/>
       <c r="E8" s="16" t="n"/>
-      <c r="F8" s="22">
+      <c r="F8" s="16" t="n"/>
+      <c r="G8" s="22">
         <f>IF(A8="","",COUNTIF(Plans!$A$3:$A$300,A8))</f>
         <v/>
       </c>
@@ -1832,7 +1859,8 @@
       <c r="C9" s="16" t="n"/>
       <c r="D9" s="16" t="n"/>
       <c r="E9" s="16" t="n"/>
-      <c r="F9" s="22">
+      <c r="F9" s="16" t="n"/>
+      <c r="G9" s="22">
         <f>IF(A9="","",COUNTIF(Plans!$A$3:$A$300,A9))</f>
         <v/>
       </c>
@@ -1843,7 +1871,8 @@
       <c r="C10" s="16" t="n"/>
       <c r="D10" s="16" t="n"/>
       <c r="E10" s="16" t="n"/>
-      <c r="F10" s="22">
+      <c r="F10" s="16" t="n"/>
+      <c r="G10" s="22">
         <f>IF(A10="","",COUNTIF(Plans!$A$3:$A$300,A10))</f>
         <v/>
       </c>
@@ -1854,7 +1883,8 @@
       <c r="C11" s="16" t="n"/>
       <c r="D11" s="16" t="n"/>
       <c r="E11" s="16" t="n"/>
-      <c r="F11" s="22">
+      <c r="F11" s="16" t="n"/>
+      <c r="G11" s="22">
         <f>IF(A11="","",COUNTIF(Plans!$A$3:$A$300,A11))</f>
         <v/>
       </c>
@@ -1865,7 +1895,8 @@
       <c r="C12" s="16" t="n"/>
       <c r="D12" s="16" t="n"/>
       <c r="E12" s="16" t="n"/>
-      <c r="F12" s="22">
+      <c r="F12" s="16" t="n"/>
+      <c r="G12" s="22">
         <f>IF(A12="","",COUNTIF(Plans!$A$3:$A$300,A12))</f>
         <v/>
       </c>
@@ -1876,7 +1907,8 @@
       <c r="C13" s="16" t="n"/>
       <c r="D13" s="16" t="n"/>
       <c r="E13" s="16" t="n"/>
-      <c r="F13" s="22">
+      <c r="F13" s="16" t="n"/>
+      <c r="G13" s="22">
         <f>IF(A13="","",COUNTIF(Plans!$A$3:$A$300,A13))</f>
         <v/>
       </c>
@@ -1887,7 +1919,8 @@
       <c r="C14" s="16" t="n"/>
       <c r="D14" s="16" t="n"/>
       <c r="E14" s="16" t="n"/>
-      <c r="F14" s="22">
+      <c r="F14" s="16" t="n"/>
+      <c r="G14" s="22">
         <f>IF(A14="","",COUNTIF(Plans!$A$3:$A$300,A14))</f>
         <v/>
       </c>
@@ -1898,7 +1931,8 @@
       <c r="C15" s="16" t="n"/>
       <c r="D15" s="16" t="n"/>
       <c r="E15" s="16" t="n"/>
-      <c r="F15" s="22">
+      <c r="F15" s="16" t="n"/>
+      <c r="G15" s="22">
         <f>IF(A15="","",COUNTIF(Plans!$A$3:$A$300,A15))</f>
         <v/>
       </c>
@@ -1909,7 +1943,8 @@
       <c r="C16" s="16" t="n"/>
       <c r="D16" s="16" t="n"/>
       <c r="E16" s="16" t="n"/>
-      <c r="F16" s="22">
+      <c r="F16" s="16" t="n"/>
+      <c r="G16" s="22">
         <f>IF(A16="","",COUNTIF(Plans!$A$3:$A$300,A16))</f>
         <v/>
       </c>
@@ -1920,7 +1955,8 @@
       <c r="C17" s="16" t="n"/>
       <c r="D17" s="16" t="n"/>
       <c r="E17" s="16" t="n"/>
-      <c r="F17" s="22">
+      <c r="F17" s="16" t="n"/>
+      <c r="G17" s="22">
         <f>IF(A17="","",COUNTIF(Plans!$A$3:$A$300,A17))</f>
         <v/>
       </c>
@@ -1931,7 +1967,8 @@
       <c r="C18" s="16" t="n"/>
       <c r="D18" s="16" t="n"/>
       <c r="E18" s="16" t="n"/>
-      <c r="F18" s="22">
+      <c r="F18" s="16" t="n"/>
+      <c r="G18" s="22">
         <f>IF(A18="","",COUNTIF(Plans!$A$3:$A$300,A18))</f>
         <v/>
       </c>
@@ -1942,7 +1979,8 @@
       <c r="C19" s="16" t="n"/>
       <c r="D19" s="16" t="n"/>
       <c r="E19" s="16" t="n"/>
-      <c r="F19" s="22">
+      <c r="F19" s="16" t="n"/>
+      <c r="G19" s="22">
         <f>IF(A19="","",COUNTIF(Plans!$A$3:$A$300,A19))</f>
         <v/>
       </c>
@@ -1953,7 +1991,8 @@
       <c r="C20" s="16" t="n"/>
       <c r="D20" s="16" t="n"/>
       <c r="E20" s="16" t="n"/>
-      <c r="F20" s="22">
+      <c r="F20" s="16" t="n"/>
+      <c r="G20" s="22">
         <f>IF(A20="","",COUNTIF(Plans!$A$3:$A$300,A20))</f>
         <v/>
       </c>
@@ -1964,7 +2003,8 @@
       <c r="C21" s="16" t="n"/>
       <c r="D21" s="16" t="n"/>
       <c r="E21" s="16" t="n"/>
-      <c r="F21" s="22">
+      <c r="F21" s="16" t="n"/>
+      <c r="G21" s="22">
         <f>IF(A21="","",COUNTIF(Plans!$A$3:$A$300,A21))</f>
         <v/>
       </c>
@@ -1975,7 +2015,8 @@
       <c r="C22" s="16" t="n"/>
       <c r="D22" s="16" t="n"/>
       <c r="E22" s="16" t="n"/>
-      <c r="F22" s="22">
+      <c r="F22" s="16" t="n"/>
+      <c r="G22" s="22">
         <f>IF(A22="","",COUNTIF(Plans!$A$3:$A$300,A22))</f>
         <v/>
       </c>
@@ -1986,7 +2027,8 @@
       <c r="C23" s="16" t="n"/>
       <c r="D23" s="16" t="n"/>
       <c r="E23" s="16" t="n"/>
-      <c r="F23" s="22">
+      <c r="F23" s="16" t="n"/>
+      <c r="G23" s="22">
         <f>IF(A23="","",COUNTIF(Plans!$A$3:$A$300,A23))</f>
         <v/>
       </c>

--- a/data/firms/futureselite.xlsx
+++ b/data/firms/futureselite.xlsx
@@ -1295,7 +1295,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="B4" s="16" t="inlineStr">
         <is>
-          <t>https://www.google.com/s2/favicons?domain=futureselite.com&amp;sz=128</t>
+          <t>https://cdn.prod.website-files.com/690a53b4dc85f8bf1d3328d4/690a53b4dc85f8bf1d332987_Webclip.svg</t>
         </is>
       </c>
       <c r="C4" s="17" t="inlineStr">
@@ -1417,186 +1417,211 @@
     <row r="6" ht="44" customHeight="1">
       <c r="A6" s="15" t="inlineStr">
         <is>
-          <t>presentation</t>
+          <t>resume</t>
         </is>
       </c>
       <c r="B6" s="16" t="inlineStr">
         <is>
-          <t>FuturesElite sells simulated futures accounts across four programs. Elite and Prime are evaluation routes with a one-time fee and no deadline to pass. Nitro and Instant shorten or remove the evaluation entirely, Instant funding you from purchase with no objective to reach. Elite, Nitro and Prime settle at a 90% profit split; Instant pays 80%. Payouts can be requested daily once an account is funded, subject to each program’s own minimum days.
-It suits futures traders who already have a method and want to choose the rule set that fits it, rather than accept one. Loss limits are dollar amounts rather than percentages, drawdown is calculated at the end of the day on the evaluation programs, and six platforms are selectable at purchase, including Tradovate, NinjaTrader and Quantower.
-The caveat matters more than the pricing. Quantum SRL holds no financial regulator licence, and every account is simulated: performance is hypothetical throughout. The live trading program exists but is a risk-team decision, not an entitlement earned at a fixed number of payouts.</t>
+          <t>FuturesElite sells simulated futures accounts across four programs. Elite, Nitro and Prime settle at a 90% profit split; Instant pays 80%.</t>
         </is>
       </c>
       <c r="C6" s="17" t="inlineStr">
         <is>
-          <t>FuturesElite sells simulated futures accounts across four programs. Elite and Prime are evaluation routes with a one-time fee and no deadline to pass.</t>
+          <t>Elite and Prime are evaluation routes with a one-time fee and no deadline to pass. Nitro and Instant shorten or remove the evaluation entirely, Instant funding you from purchase with no objective to reach.</t>
         </is>
       </c>
       <c r="D6" s="18" t="inlineStr">
         <is>
-          <t>Le texte sous le nom. Factuel et developpe : separe les paragraphes par une ligne vide (Alt+Entree deux fois).</t>
+          <t>En haut de page, sous le nom : 1 a 2 phrases. Le detail va dans presentation.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="44" customHeight="1">
       <c r="A7" s="15" t="inlineStr">
         <is>
-          <t>annee_creation</t>
-        </is>
-      </c>
-      <c r="B7" s="19" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C7" s="20" t="n">
-        <v>2024</v>
+          <t>presentation</t>
+        </is>
+      </c>
+      <c r="B7" s="16" t="inlineStr">
+        <is>
+          <t>It suits futures traders who already have a method and want to choose the rule set that fits it, rather than accept one. Loss limits are dollar amounts rather than percentages, drawdown is calculated at the end of the day on the evaluation programs, and six platforms are selectable at purchase, including Tradovate, NinjaTrader and Quantower.
+The caveat matters more than the pricing. Quantum SRL holds no financial regulator licence, and every account is simulated: performance is hypothetical throughout. The live trading program exists but is a risk-team decision, not an entitlement earned at a fixed number of payouts.</t>
+        </is>
+      </c>
+      <c r="C7" s="17" t="inlineStr">
+        <is>
+          <t>FuturesElite sells simulated futures accounts across four programs. Elite and Prime are evaluation routes with a one-time fee and no deadline to pass.</t>
+        </is>
       </c>
       <c r="D7" s="18" t="inlineStr">
         <is>
-          <t>« Founded ». Vide : « — ».</t>
+          <t>Section « About [Firm] » : texte developpe, paragraphes separes par une ligne vide (Alt+Entree deux fois).</t>
         </is>
       </c>
     </row>
     <row r="8" ht="44" customHeight="1">
       <c r="A8" s="15" t="inlineStr">
         <is>
-          <t>pays</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
-        <is>
-          <t>Italy</t>
-        </is>
-      </c>
-      <c r="C8" s="17" t="inlineStr">
-        <is>
-          <t>Italy</t>
-        </is>
+          <t>annee_creation</t>
+        </is>
+      </c>
+      <c r="B8" s="19" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C8" s="20" t="n">
+        <v>2024</v>
       </c>
       <c r="D8" s="18" t="inlineStr">
         <is>
-          <t>« Country ».</t>
+          <t>« Founded ». Vide : « — ».</t>
         </is>
       </c>
     </row>
     <row r="9" ht="44" customHeight="1">
       <c r="A9" s="15" t="inlineStr">
         <is>
-          <t>ceo_fondateur</t>
+          <t>pays</t>
         </is>
       </c>
       <c r="B9" s="16" t="inlineStr">
         <is>
-          <t>Christian Habibi</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="C9" s="17" t="inlineStr">
         <is>
-          <t>Christian Habibi</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="D9" s="18" t="inlineStr">
         <is>
-          <t>« CEO / Founder ». Vide : « — ».</t>
+          <t>« Country ».</t>
         </is>
       </c>
     </row>
     <row r="10" ht="44" customHeight="1">
       <c r="A10" s="15" t="inlineStr">
         <is>
-          <t>actifs</t>
+          <t>ceo_fondateur</t>
         </is>
       </c>
       <c r="B10" s="16" t="inlineStr">
         <is>
-          <t>Futures, Forex, Metals, Indices, Energy, Crypto, Bonds, Agricultural Products</t>
+          <t>Christian Habibi</t>
         </is>
       </c>
       <c r="C10" s="17" t="inlineStr">
         <is>
-          <t>Futures, Forex, Metals, Indices, Energy, Crypto, Bonds, Agricultural Products</t>
+          <t>Christian Habibi</t>
         </is>
       </c>
       <c r="D10" s="18" t="inlineStr">
         <is>
-          <t>« Tradable assets » : une etiquette par actif, separes par des virgules.</t>
+          <t>« CEO / Founder ». Vide : « — ».</t>
         </is>
       </c>
     </row>
     <row r="11" ht="44" customHeight="1">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>plateformes</t>
+          <t>actifs</t>
         </is>
       </c>
       <c r="B11" s="16" t="inlineStr">
         <is>
-          <t>Tradovate, NinjaTrader, Quantower, ATAS, WealthCharts, DeepChart</t>
+          <t>Futures, Forex, Metals, Indices, Energy, Crypto, Bonds, Agricultural Products</t>
         </is>
       </c>
       <c r="C11" s="17" t="inlineStr">
         <is>
-          <t>Tradovate, NinjaTrader, Quantower, ATAS, WealthCharts, DeepChart</t>
+          <t>Futures, Forex, Metals, Indices, Energy, Crypto, Bonds, Agricultural Products</t>
         </is>
       </c>
       <c r="D11" s="18" t="inlineStr">
         <is>
-          <t>« Platforms » : celles choisies A L'ACHAT, separees par des virgules.</t>
+          <t>« Tradable assets » (« Futures markets » chez une firme 100 % futures) : une etiquette par actif, separes par des virgules.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="44" customHeight="1">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>moyens_paiement</t>
+          <t>plateformes</t>
         </is>
       </c>
       <c r="B12" s="16" t="inlineStr">
         <is>
-          <t>Credit/Debit Card, Crypto</t>
+          <t>Tradovate, NinjaTrader, Quantower, ATAS, WealthCharts, DeepChart, Volumetrica, DeepCharts</t>
         </is>
       </c>
       <c r="C12" s="17" t="inlineStr">
         <is>
-          <t>Credit/Debit Card, Crypto</t>
+          <t>Tradovate, NinjaTrader, Quantower, ATAS, WealthCharts, DeepChart, Volumetrica, DeepCharts</t>
         </is>
       </c>
       <c r="D12" s="18" t="inlineStr">
         <is>
-          <t>« Payment methods » : moyens de paiement a l'achat (carte, crypto…). Ceux des retraits vont dans Conditions &gt; retraits.</t>
+          <t>« Platforms » : toutes les plateformes prises en charge, separees par des virgules.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="44" customHeight="1">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>levier</t>
-        </is>
-      </c>
-      <c r="B13" s="16" t="n"/>
+          <t>moyens_paiement</t>
+        </is>
+      </c>
+      <c r="B13" s="16" t="inlineStr">
+        <is>
+          <t>Credit/Debit Card, Crypto</t>
+        </is>
+      </c>
       <c r="C13" s="17" t="inlineStr">
         <is>
-          <t>(vide — futures : exposition en contrats, pas en levier)</t>
+          <t>Credit/Debit Card, Crypto</t>
         </is>
       </c>
       <c r="D13" s="18" t="inlineStr">
         <is>
-          <t>« Trading profile » : « Leverage 1:X ». Vide : « Leverage — ».</t>
+          <t>« Payment methods » : moyens de paiement a l'achat (carte, crypto…). Ceux des retraits vont dans Conditions &gt; retraits.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="44" customHeight="1">
       <c r="A14" s="15" t="inlineStr">
         <is>
+          <t>levier</t>
+        </is>
+      </c>
+      <c r="B14" s="16" t="inlineStr">
+        <is>
+          <t>N/A (futures contracts)</t>
+        </is>
+      </c>
+      <c r="C14" s="17" t="inlineStr">
+        <is>
+          <t>N/A (futures contracts)</t>
+        </is>
+      </c>
+      <c r="D14" s="18" t="inlineStr">
+        <is>
+          <t>« Trading profile » : « Leverage 1:X ». Vide : « Leverage — ».</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="44" customHeight="1">
+      <c r="A15" s="15" t="inlineStr">
+        <is>
           <t>styles_trading</t>
         </is>
       </c>
-      <c r="B14" s="16" t="n"/>
-      <c r="C14" s="17" t="inlineStr">
+      <c r="B15" s="16" t="n"/>
+      <c r="C15" s="17" t="inlineStr">
         <is>
           <t>(vide — absent du releve)</t>
         </is>
       </c>
-      <c r="D14" s="18" t="inlineStr">
+      <c r="D15" s="18" t="inlineStr">
         <is>
           <t>« Trading profile » : styles autorises (Swing…), separes par des virgules.</t>
         </is>
@@ -1615,7 +1640,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:H23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1624,7 +1649,8 @@
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="32" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -1660,6 +1686,11 @@
       </c>
       <c r="G1" s="14" t="inlineStr">
         <is>
+          <t>resume</t>
+        </is>
+      </c>
+      <c r="H1" s="14" t="inlineStr">
+        <is>
           <t>nb_plans  (auto)</t>
         </is>
       </c>
@@ -1697,6 +1728,11 @@
       </c>
       <c r="G2" s="21" t="inlineStr">
         <is>
+          <t>Carte « Which program fits you? » : une phrase vraie de CE programme. Vide : la carte n'affiche que le nom.</t>
+        </is>
+      </c>
+      <c r="H2" s="21" t="inlineStr">
+        <is>
           <t>Plans rattaches.</t>
         </is>
       </c>
@@ -1727,8 +1763,17 @@
           <t>active</t>
         </is>
       </c>
-      <c r="F3" s="16" t="n"/>
-      <c r="G3" s="22">
+      <c r="F3" s="16" t="inlineStr">
+        <is>
+          <t>One-step evaluation</t>
+        </is>
+      </c>
+      <c r="G3" s="16" t="inlineStr">
+        <is>
+          <t>One-step evaluation, end-of-day drawdown and no daily loss limit.</t>
+        </is>
+      </c>
+      <c r="H3" s="22">
         <f>IF(A3="","",COUNTIF(Plans!$A$3:$A$300,A3))</f>
         <v/>
       </c>
@@ -1759,8 +1804,17 @@
           <t>active</t>
         </is>
       </c>
-      <c r="F4" s="16" t="n"/>
-      <c r="G4" s="22">
+      <c r="F4" s="16" t="inlineStr">
+        <is>
+          <t>Lowest minimum trading days</t>
+        </is>
+      </c>
+      <c r="G4" s="16" t="inlineStr">
+        <is>
+          <t>One-step evaluation with the lowest minimum trading days. Once funded it switches to a trailing-equity drawdown with a buffer.</t>
+        </is>
+      </c>
+      <c r="H4" s="22">
         <f>IF(A4="","",COUNTIF(Plans!$A$3:$A$300,A4))</f>
         <v/>
       </c>
@@ -1791,8 +1845,17 @@
           <t>active</t>
         </is>
       </c>
-      <c r="F5" s="16" t="n"/>
-      <c r="G5" s="22">
+      <c r="F5" s="16" t="inlineStr">
+        <is>
+          <t>Up to 10 funded accounts</t>
+        </is>
+      </c>
+      <c r="G5" s="16" t="inlineStr">
+        <is>
+          <t>The only programme with a daily loss limit in both phases. It also carries the longest bundle ladder, up to ten accounts.</t>
+        </is>
+      </c>
+      <c r="H5" s="22">
         <f>IF(A5="","",COUNTIF(Plans!$A$3:$A$300,A5))</f>
         <v/>
       </c>
@@ -1823,8 +1886,17 @@
           <t>active</t>
         </is>
       </c>
-      <c r="F6" s="16" t="n"/>
-      <c r="G6" s="22">
+      <c r="F6" s="16" t="inlineStr">
+        <is>
+          <t>Live from purchase</t>
+        </is>
+      </c>
+      <c r="G6" s="16" t="inlineStr">
+        <is>
+          <t>No evaluation: the account is live from purchase. Payout eligibility still requires 10 trading days and a 20% consistency rule.</t>
+        </is>
+      </c>
+      <c r="H6" s="22">
         <f>IF(A6="","",COUNTIF(Plans!$A$3:$A$300,A6))</f>
         <v/>
       </c>
@@ -1836,7 +1908,8 @@
       <c r="D7" s="16" t="n"/>
       <c r="E7" s="16" t="n"/>
       <c r="F7" s="16" t="n"/>
-      <c r="G7" s="22">
+      <c r="G7" s="16" t="n"/>
+      <c r="H7" s="22">
         <f>IF(A7="","",COUNTIF(Plans!$A$3:$A$300,A7))</f>
         <v/>
       </c>
@@ -1848,7 +1921,8 @@
       <c r="D8" s="16" t="n"/>
       <c r="E8" s="16" t="n"/>
       <c r="F8" s="16" t="n"/>
-      <c r="G8" s="22">
+      <c r="G8" s="16" t="n"/>
+      <c r="H8" s="22">
         <f>IF(A8="","",COUNTIF(Plans!$A$3:$A$300,A8))</f>
         <v/>
       </c>
@@ -1860,7 +1934,8 @@
       <c r="D9" s="16" t="n"/>
       <c r="E9" s="16" t="n"/>
       <c r="F9" s="16" t="n"/>
-      <c r="G9" s="22">
+      <c r="G9" s="16" t="n"/>
+      <c r="H9" s="22">
         <f>IF(A9="","",COUNTIF(Plans!$A$3:$A$300,A9))</f>
         <v/>
       </c>
@@ -1872,7 +1947,8 @@
       <c r="D10" s="16" t="n"/>
       <c r="E10" s="16" t="n"/>
       <c r="F10" s="16" t="n"/>
-      <c r="G10" s="22">
+      <c r="G10" s="16" t="n"/>
+      <c r="H10" s="22">
         <f>IF(A10="","",COUNTIF(Plans!$A$3:$A$300,A10))</f>
         <v/>
       </c>
@@ -1884,7 +1960,8 @@
       <c r="D11" s="16" t="n"/>
       <c r="E11" s="16" t="n"/>
       <c r="F11" s="16" t="n"/>
-      <c r="G11" s="22">
+      <c r="G11" s="16" t="n"/>
+      <c r="H11" s="22">
         <f>IF(A11="","",COUNTIF(Plans!$A$3:$A$300,A11))</f>
         <v/>
       </c>
@@ -1896,7 +1973,8 @@
       <c r="D12" s="16" t="n"/>
       <c r="E12" s="16" t="n"/>
       <c r="F12" s="16" t="n"/>
-      <c r="G12" s="22">
+      <c r="G12" s="16" t="n"/>
+      <c r="H12" s="22">
         <f>IF(A12="","",COUNTIF(Plans!$A$3:$A$300,A12))</f>
         <v/>
       </c>
@@ -1908,7 +1986,8 @@
       <c r="D13" s="16" t="n"/>
       <c r="E13" s="16" t="n"/>
       <c r="F13" s="16" t="n"/>
-      <c r="G13" s="22">
+      <c r="G13" s="16" t="n"/>
+      <c r="H13" s="22">
         <f>IF(A13="","",COUNTIF(Plans!$A$3:$A$300,A13))</f>
         <v/>
       </c>
@@ -1920,7 +1999,8 @@
       <c r="D14" s="16" t="n"/>
       <c r="E14" s="16" t="n"/>
       <c r="F14" s="16" t="n"/>
-      <c r="G14" s="22">
+      <c r="G14" s="16" t="n"/>
+      <c r="H14" s="22">
         <f>IF(A14="","",COUNTIF(Plans!$A$3:$A$300,A14))</f>
         <v/>
       </c>
@@ -1932,7 +2012,8 @@
       <c r="D15" s="16" t="n"/>
       <c r="E15" s="16" t="n"/>
       <c r="F15" s="16" t="n"/>
-      <c r="G15" s="22">
+      <c r="G15" s="16" t="n"/>
+      <c r="H15" s="22">
         <f>IF(A15="","",COUNTIF(Plans!$A$3:$A$300,A15))</f>
         <v/>
       </c>
@@ -1944,7 +2025,8 @@
       <c r="D16" s="16" t="n"/>
       <c r="E16" s="16" t="n"/>
       <c r="F16" s="16" t="n"/>
-      <c r="G16" s="22">
+      <c r="G16" s="16" t="n"/>
+      <c r="H16" s="22">
         <f>IF(A16="","",COUNTIF(Plans!$A$3:$A$300,A16))</f>
         <v/>
       </c>
@@ -1956,7 +2038,8 @@
       <c r="D17" s="16" t="n"/>
       <c r="E17" s="16" t="n"/>
       <c r="F17" s="16" t="n"/>
-      <c r="G17" s="22">
+      <c r="G17" s="16" t="n"/>
+      <c r="H17" s="22">
         <f>IF(A17="","",COUNTIF(Plans!$A$3:$A$300,A17))</f>
         <v/>
       </c>
@@ -1968,7 +2051,8 @@
       <c r="D18" s="16" t="n"/>
       <c r="E18" s="16" t="n"/>
       <c r="F18" s="16" t="n"/>
-      <c r="G18" s="22">
+      <c r="G18" s="16" t="n"/>
+      <c r="H18" s="22">
         <f>IF(A18="","",COUNTIF(Plans!$A$3:$A$300,A18))</f>
         <v/>
       </c>
@@ -1980,7 +2064,8 @@
       <c r="D19" s="16" t="n"/>
       <c r="E19" s="16" t="n"/>
       <c r="F19" s="16" t="n"/>
-      <c r="G19" s="22">
+      <c r="G19" s="16" t="n"/>
+      <c r="H19" s="22">
         <f>IF(A19="","",COUNTIF(Plans!$A$3:$A$300,A19))</f>
         <v/>
       </c>
@@ -1992,7 +2077,8 @@
       <c r="D20" s="16" t="n"/>
       <c r="E20" s="16" t="n"/>
       <c r="F20" s="16" t="n"/>
-      <c r="G20" s="22">
+      <c r="G20" s="16" t="n"/>
+      <c r="H20" s="22">
         <f>IF(A20="","",COUNTIF(Plans!$A$3:$A$300,A20))</f>
         <v/>
       </c>
@@ -2004,7 +2090,8 @@
       <c r="D21" s="16" t="n"/>
       <c r="E21" s="16" t="n"/>
       <c r="F21" s="16" t="n"/>
-      <c r="G21" s="22">
+      <c r="G21" s="16" t="n"/>
+      <c r="H21" s="22">
         <f>IF(A21="","",COUNTIF(Plans!$A$3:$A$300,A21))</f>
         <v/>
       </c>
@@ -2016,7 +2103,8 @@
       <c r="D22" s="16" t="n"/>
       <c r="E22" s="16" t="n"/>
       <c r="F22" s="16" t="n"/>
-      <c r="G22" s="22">
+      <c r="G22" s="16" t="n"/>
+      <c r="H22" s="22">
         <f>IF(A22="","",COUNTIF(Plans!$A$3:$A$300,A22))</f>
         <v/>
       </c>
@@ -2028,7 +2116,8 @@
       <c r="D23" s="16" t="n"/>
       <c r="E23" s="16" t="n"/>
       <c r="F23" s="16" t="n"/>
-      <c r="G23" s="22">
+      <c r="G23" s="16" t="n"/>
+      <c r="H23" s="22">
         <f>IF(A23="","",COUNTIF(Plans!$A$3:$A$300,A23))</f>
         <v/>
       </c>

--- a/data/firms/futureselite.xlsx
+++ b/data/firms/futureselite.xlsx
@@ -14,9 +14,11 @@
     <sheet name="Phases" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Offre" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="Conditions" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Verdict" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="FAQ" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Listes" sheetId="10" state="hidden" r:id="rId10"/>
+    <sheet name="Parcours" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Couts" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Verdict" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="FAQ" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Listes" sheetId="12" state="hidden" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -319,6 +321,21 @@
 </comments>
 </file>
 
+<file path=xl/comments/comment10.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>PropFirmScanner</author>
+  </authors>
+  <commentList>
+    <comment ref="C3" authorId="0" shapeId="0">
+      <text>
+        <t>Le releve FuturesElite du 7 septembre 2026 ne contient aucune FAQ : aucune reponse d'exemple n'a ete inventee.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/comments/comment2.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
@@ -420,9 +437,24 @@
     <author>PropFirmScanner</author>
   </authors>
   <commentList>
-    <comment ref="C3" authorId="0" shapeId="0">
+    <comment ref="A3" authorId="0" shapeId="0">
       <text>
-        <t>Le releve FuturesElite du 7 septembre 2026 ne contient aucune FAQ : aucune reponse d'exemple n'a ete inventee.</t>
+        <t>Exemple : valeurs reelles FuturesElite, releve du 7 septembre 2026. A remplacer.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment9.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>PropFirmScanner</author>
+  </authors>
+  <commentList>
+    <comment ref="A3" authorId="0" shapeId="0">
+      <text>
+        <t>Exemple : valeurs reelles FuturesElite, releve du 7 septembre 2026. A remplacer.</t>
       </text>
     </comment>
   </commentList>
@@ -719,7 +751,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:D32"/>
+  <dimension ref="B2:D34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -867,122 +899,114 @@
     <row r="17" ht="30" customHeight="1">
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>Verdict</t>
+          <t>Parcours</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>« Who we recommend [Firm] for » : verdict, bons profils, « Consider another firm if… » · « Strengths and things to know » : points forts et limites</t>
+          <t>« From evaluation to your first payout » : les etapes, dans l'ordre</t>
         </is>
       </c>
     </row>
     <row r="18" ht="30" customHeight="1">
       <c r="B18" s="9" t="inlineStr">
         <is>
+          <t>Couts</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>« What you will actually pay » : le tableau des frais</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="30" customHeight="1">
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>Verdict</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>« Who we recommend [Firm] for » : verdict, bons profils, « Consider another firm if… » · « Strengths and things to know » : points forts et limites</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="30" customHeight="1">
+      <c r="B20" s="9" t="inlineStr">
+        <is>
           <t>FAQ</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
+      <c r="C20" s="5" t="inlineStr">
         <is>
           <t>« Frequently asked questions » : les 5 questions du gabarit sont deja ecrites, il reste les reponses</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="B20" s="3" t="inlineStr">
+    <row r="22">
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>LES REGLES QUI EVITENT LES ERREURS</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="30" customHeight="1">
-      <c r="B21" s="9" t="inlineStr">
-        <is>
-          <t>Un plan, plusieurs phases</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>Un plan = programme + variante + taille (onglet Plans). Ses phases Evaluation et Funded vont dans l'onglet Phases, une ligne chacune.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="30" customHeight="1">
-      <c r="B22" s="9" t="inlineStr">
-        <is>
-          <t>Un seul plan dans la carte promo</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>Mets « oui » dans plan_carte_promo sur UN seul plan : c'est lui qui s'affiche dans la carte en haut de page.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="30" customHeight="1">
       <c r="B23" s="9" t="inlineStr">
         <is>
+          <t>Un plan, plusieurs phases</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>Un plan = programme + variante + taille (onglet Plans). Ses phases Evaluation et Funded vont dans l'onglet Phases, une ligne chacune.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="30" customHeight="1">
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>Un seul plan dans la carte promo</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>Mets « oui » dans plan_carte_promo sur UN seul plan : c'est lui qui s'affiche dans la carte en haut de page.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="30" customHeight="1">
+      <c r="B25" s="9" t="inlineStr">
+        <is>
           <t>Un code promo non confirme</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr">
+      <c r="C25" s="5" t="inlineStr">
         <is>
           <t>Si sa portee n'est pas confirmee, le prix remise s'affiche avec « ≈ » devant.</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="B25" s="3" t="inlineStr">
+    <row r="27">
+      <c r="B27" s="3" t="inlineStr">
         <is>
           <t>CONTROLES AUTOMATIQUES</t>
         </is>
       </c>
-      <c r="D25" s="10" t="inlineStr">
+      <c r="D27" s="10" t="inlineStr">
         <is>
           <t>attendu</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="11" t="inlineStr">
-        <is>
-          <t>Programmes</t>
-        </is>
-      </c>
-      <c r="C26" s="12">
-        <f>COUNTA(Programmes!A3:A60)</f>
-        <v/>
-      </c>
-      <c r="D26" s="13" t="inlineStr">
-        <is>
-          <t>≥ 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="11" t="inlineStr">
-        <is>
-          <t>Plans (selections)</t>
-        </is>
-      </c>
-      <c r="C27" s="12">
-        <f>COUNTA(Plans!A3:A300)</f>
-        <v/>
-      </c>
-      <c r="D27" s="13" t="inlineStr">
-        <is>
-          <t>≥ 1</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>Phases</t>
+          <t>Programmes</t>
         </is>
       </c>
       <c r="C28" s="12">
-        <f>COUNTA(Phases!A3:A900)</f>
+        <f>COUNTA(Programmes!A3:A60)</f>
         <v/>
       </c>
       <c r="D28" s="13" t="inlineStr">
@@ -994,62 +1018,94 @@
     <row r="29">
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>Plans dans la carte promo</t>
+          <t>Plans (selections)</t>
         </is>
       </c>
       <c r="C29" s="12">
-        <f>COUNTIF(Plans!F3:F300,"oui")</f>
+        <f>COUNTA(Plans!A3:A300)</f>
         <v/>
       </c>
       <c r="D29" s="13" t="inlineStr">
         <is>
-          <t>exactement 1</t>
+          <t>≥ 1</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>Phases sans plan correspondant</t>
+          <t>Phases</t>
         </is>
       </c>
       <c r="C30" s="12">
-        <f>COUNTIF(Phases!M3:M900,"PLAN INCONNU")</f>
+        <f>COUNTA(Phases!A3:A900)</f>
         <v/>
       </c>
       <c r="D30" s="13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>≥ 1</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>Plans sans aucune phase</t>
+          <t>Plans dans la carte promo</t>
         </is>
       </c>
       <c r="C31" s="12">
-        <f>COUNTIF(Plans!H3:H300,"aucune phase")</f>
+        <f>COUNTIF(Plans!F3:F300,"oui")</f>
         <v/>
       </c>
       <c r="D31" s="13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>exactement 1</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="B32" s="11" t="inlineStr">
         <is>
+          <t>Phases sans plan correspondant</t>
+        </is>
+      </c>
+      <c r="C32" s="12">
+        <f>COUNTIF(Phases!M3:M900,"PLAN INCONNU")</f>
+        <v/>
+      </c>
+      <c r="D32" s="13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="11" t="inlineStr">
+        <is>
+          <t>Plans sans aucune phase</t>
+        </is>
+      </c>
+      <c r="C33" s="12">
+        <f>COUNTIF(Plans!H3:H300,"aucune phase")</f>
+        <v/>
+      </c>
+      <c r="D33" s="13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="11" t="inlineStr">
+        <is>
           <t>Plans d'un programme inconnu</t>
         </is>
       </c>
-      <c r="C32" s="12">
+      <c r="C34" s="12">
         <f>COUNTIF(Plans!H3:H300,"programme inconnu")</f>
         <v/>
       </c>
-      <c r="D32" s="13" t="inlineStr">
+      <c r="D34" s="13" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1063,11 +1119,641 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="006B7280"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C37"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="96" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="14" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="B1" s="14" t="inlineStr">
+        <is>
+          <t>ordre</t>
+        </is>
+      </c>
+      <c r="C1" s="14" t="inlineStr">
+        <is>
+          <t>texte</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="58" customHeight="1">
+      <c r="A2" s="21" t="inlineStr">
+        <is>
+          <t>verdict = « Our verdict » · pour_qui = liste ✓ · pas_pour = « Consider another firm if… » · point_fort = « Strengths » · limite = « Things to know »</t>
+        </is>
+      </c>
+      <c r="B2" s="21" t="inlineStr">
+        <is>
+          <t>1, 2, 3 dans chaque type. Le gabarit en montre 3.</t>
+        </is>
+      </c>
+      <c r="C2" s="21" t="inlineStr">
+        <is>
+          <t>Conclusion independante, sans superlatif marketing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="16" t="inlineStr">
+        <is>
+          <t>verdict</t>
+        </is>
+      </c>
+      <c r="B3" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="16" t="inlineStr">
+        <is>
+          <t>FuturesElite bets on generous terms once you are funded: up to a 90% split, daily payouts, and no funded consistency rule on Elite and Nitro. In exchange, the firm is young and is a proprietary trading company rather than a regulated broker.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="16" t="inlineStr">
+        <is>
+          <t>pour_qui</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="16" t="inlineStr">
+        <is>
+          <t>A high split and frequent payouts, with no waiting period</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="16" t="inlineStr">
+        <is>
+          <t>pour_qui</t>
+        </is>
+      </c>
+      <c r="B5" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" s="16" t="inlineStr">
+        <is>
+          <t>Elite or Nitro evaluations without a daily loss limit, which leaves room to breathe</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="16" t="inlineStr">
+        <is>
+          <t>pour_qui</t>
+        </is>
+      </c>
+      <c r="B6" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="C6" s="16" t="inlineStr">
+        <is>
+          <t>A funded account that opens with no activation fee</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="16" t="inlineStr">
+        <is>
+          <t>pour_qui</t>
+        </is>
+      </c>
+      <c r="B7" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="C7" s="16" t="inlineStr">
+        <is>
+          <t>The option to stack up to ten accounts in parallel</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="16" t="inlineStr">
+        <is>
+          <t>pas_pour</t>
+        </is>
+      </c>
+      <c r="B8" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" s="16" t="inlineStr">
+        <is>
+          <t>You want a regulated broker: Quantum SRL holds no financial regulator licence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="16" t="inlineStr">
+        <is>
+          <t>pas_pour</t>
+        </is>
+      </c>
+      <c r="B9" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="C9" s="16" t="inlineStr">
+        <is>
+          <t>You want real capital: every account is simulated, and performance stays hypothetical.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="16" t="inlineStr">
+        <is>
+          <t>pas_pour</t>
+        </is>
+      </c>
+      <c r="B10" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="C10" s="16" t="inlineStr">
+        <is>
+          <t>You run fully automated systems: AI and bots are prohibited.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="16" t="inlineStr">
+        <is>
+          <t>pas_pour</t>
+        </is>
+      </c>
+      <c r="B11" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="C11" s="16" t="inlineStr">
+        <is>
+          <t>You want to withdraw a whole balance at once: each request is capped by account size.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="16" t="inlineStr">
+        <is>
+          <t>pas_pour</t>
+        </is>
+      </c>
+      <c r="B12" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="C12" s="16" t="inlineStr">
+        <is>
+          <t>You need a guaranteed route to live trading: it is a risk-team decision, not an entitlement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="16" t="inlineStr">
+        <is>
+          <t>point_fort</t>
+        </is>
+      </c>
+      <c r="B13" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" s="16" t="inlineStr">
+        <is>
+          <t>90% profit split on Elite, Nitro and Prime; 80% on Instant</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="16" t="inlineStr">
+        <is>
+          <t>point_fort</t>
+        </is>
+      </c>
+      <c r="B14" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="C14" s="16" t="inlineStr">
+        <is>
+          <t>Drawdown type differs by program and phase — see the rules table</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="16" t="inlineStr">
+        <is>
+          <t>point_fort</t>
+        </is>
+      </c>
+      <c r="B15" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="C15" s="16" t="inlineStr">
+        <is>
+          <t>No daily loss limit on Elite, Nitro and Instant — Prime has one in both phases</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="16" t="inlineStr">
+        <is>
+          <t>point_fort</t>
+        </is>
+      </c>
+      <c r="B16" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="C16" s="16" t="inlineStr">
+        <is>
+          <t>No funded consistency rule on Elite and Nitro</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="16" t="inlineStr">
+        <is>
+          <t>point_fort</t>
+        </is>
+      </c>
+      <c r="B17" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="C17" s="16" t="inlineStr">
+        <is>
+          <t>No activation fee to unlock the funded account</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="16" t="inlineStr">
+        <is>
+          <t>point_fort</t>
+        </is>
+      </c>
+      <c r="B18" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="C18" s="16" t="inlineStr">
+        <is>
+          <t>Payouts available every day once funded</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="16" t="inlineStr">
+        <is>
+          <t>point_fort</t>
+        </is>
+      </c>
+      <c r="B19" s="19" t="n">
+        <v>7</v>
+      </c>
+      <c r="C19" s="16" t="inlineStr">
+        <is>
+          <t>Bundle discounts: the fifth account is free</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="16" t="inlineStr">
+        <is>
+          <t>limite</t>
+        </is>
+      </c>
+      <c r="B20" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" s="16" t="inlineStr">
+        <is>
+          <t>No financial regulator licence</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="16" t="inlineStr">
+        <is>
+          <t>limite</t>
+        </is>
+      </c>
+      <c r="B21" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="C21" s="16" t="inlineStr">
+        <is>
+          <t>Demo accounts, hypothetical performance</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="16" t="inlineStr">
+        <is>
+          <t>limite</t>
+        </is>
+      </c>
+      <c r="B22" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="C22" s="16" t="inlineStr">
+        <is>
+          <t>Minimum days differ by program; Elite needs 6 profitable days above a size-based threshold before a payout</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="16" t="inlineStr">
+        <is>
+          <t>limite</t>
+        </is>
+      </c>
+      <c r="B23" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="C23" s="16" t="inlineStr">
+        <is>
+          <t>Per-request payout cap, from $1,000 to $3,000 by account size</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="16" t="n"/>
+      <c r="B24" s="19" t="n"/>
+      <c r="C24" s="16" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="16" t="n"/>
+      <c r="B25" s="19" t="n"/>
+      <c r="C25" s="16" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="16" t="n"/>
+      <c r="B26" s="19" t="n"/>
+      <c r="C26" s="16" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="16" t="n"/>
+      <c r="B27" s="19" t="n"/>
+      <c r="C27" s="16" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="16" t="n"/>
+      <c r="B28" s="19" t="n"/>
+      <c r="C28" s="16" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="16" t="n"/>
+      <c r="B29" s="19" t="n"/>
+      <c r="C29" s="16" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="16" t="n"/>
+      <c r="B30" s="19" t="n"/>
+      <c r="C30" s="16" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="16" t="n"/>
+      <c r="B31" s="19" t="n"/>
+      <c r="C31" s="16" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="16" t="n"/>
+      <c r="B32" s="19" t="n"/>
+      <c r="C32" s="16" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="16" t="n"/>
+      <c r="B33" s="19" t="n"/>
+      <c r="C33" s="16" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="16" t="n"/>
+      <c r="B34" s="19" t="n"/>
+      <c r="C34" s="16" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="16" t="n"/>
+      <c r="B35" s="19" t="n"/>
+      <c r="C35" s="16" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="16" t="n"/>
+      <c r="B36" s="19" t="n"/>
+      <c r="C36" s="16" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="16" t="n"/>
+      <c r="B37" s="19" t="n"/>
+      <c r="C37" s="16" t="n"/>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="A3:A37" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valeur hors liste" error="Choisis une valeur dans la liste deroulante." type="list">
+      <formula1>=Listes!$J$2:$J$6</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="006B7280"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="80" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="14" t="inlineStr">
+        <is>
+          <t>ordre</t>
+        </is>
+      </c>
+      <c r="B1" s="14" t="inlineStr">
+        <is>
+          <t>question</t>
+        </is>
+      </c>
+      <c r="C1" s="14" t="inlineStr">
+        <is>
+          <t>reponse</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="58" customHeight="1">
+      <c r="A2" s="21" t="inlineStr">
+        <is>
+          <t>Ordre d'affichage.</t>
+        </is>
+      </c>
+      <c r="B2" s="21" t="inlineStr">
+        <is>
+          <t>Les 5 questions du gabarit sont pre-remplies ; [Firm] sera remplace par le nom. Tu peux en ajouter.</t>
+        </is>
+      </c>
+      <c r="C2" s="21" t="inlineStr">
+        <is>
+          <t>Vide : la page recompose la reponse depuis les autres onglets (programmes, prix, partage, retraits, offre).</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="16" t="inlineStr">
+        <is>
+          <t>Is [Firm] suitable for beginners?</t>
+        </is>
+      </c>
+      <c r="C3" s="16" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" s="16" t="inlineStr">
+        <is>
+          <t>How much does [Firm] cost?</t>
+        </is>
+      </c>
+      <c r="C4" s="16" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" s="16" t="inlineStr">
+        <is>
+          <t>What profit split does [Firm] offer?</t>
+        </is>
+      </c>
+      <c r="C5" s="16" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" s="16" t="inlineStr">
+        <is>
+          <t>How do payouts work?</t>
+        </is>
+      </c>
+      <c r="C6" s="16" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" s="16" t="inlineStr">
+        <is>
+          <t>Does the promotional code apply to every account?</t>
+        </is>
+      </c>
+      <c r="C7" s="16" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="19" t="n"/>
+      <c r="B8" s="16" t="n"/>
+      <c r="C8" s="16" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="19" t="n"/>
+      <c r="B9" s="16" t="n"/>
+      <c r="C9" s="16" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="19" t="n"/>
+      <c r="B10" s="16" t="n"/>
+      <c r="C10" s="16" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="19" t="n"/>
+      <c r="B11" s="16" t="n"/>
+      <c r="C11" s="16" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="19" t="n"/>
+      <c r="B12" s="16" t="n"/>
+      <c r="C12" s="16" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="19" t="n"/>
+      <c r="B13" s="16" t="n"/>
+      <c r="C13" s="16" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="19" t="n"/>
+      <c r="B14" s="16" t="n"/>
+      <c r="C14" s="16" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="19" t="n"/>
+      <c r="B15" s="16" t="n"/>
+      <c r="C15" s="16" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="19" t="n"/>
+      <c r="B16" s="16" t="n"/>
+      <c r="C16" s="16" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="19" t="n"/>
+      <c r="B17" s="16" t="n"/>
+      <c r="C17" s="16" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="19" t="n"/>
+      <c r="B18" s="16" t="n"/>
+      <c r="C18" s="16" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="19" t="n"/>
+      <c r="B19" s="16" t="n"/>
+      <c r="C19" s="16" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="19" t="n"/>
+      <c r="B20" s="16" t="n"/>
+      <c r="C20" s="16" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="19" t="n"/>
+      <c r="B21" s="16" t="n"/>
+      <c r="C21" s="16" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="19" t="n"/>
+      <c r="B22" s="16" t="n"/>
+      <c r="C22" s="16" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
     <tabColor rgb="009CA3AF"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1079,50 +1765,56 @@
     <col width="20" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
+          <t>etape_parcours</t>
+        </is>
+      </c>
+      <c r="B1" s="9" t="inlineStr">
+        <is>
           <t>marche</t>
         </is>
       </c>
-      <c r="B1" s="9" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
         <is>
           <t>type_programme</t>
         </is>
       </c>
-      <c r="C1" s="9" t="inlineStr">
+      <c r="D1" s="9" t="inlineStr">
         <is>
           <t>statut</t>
         </is>
       </c>
-      <c r="D1" s="9" t="inlineStr">
+      <c r="E1" s="9" t="inlineStr">
         <is>
           <t>phase</t>
         </is>
       </c>
-      <c r="E1" s="9" t="inlineStr">
+      <c r="F1" s="9" t="inlineStr">
         <is>
           <t>type_perte</t>
         </is>
       </c>
-      <c r="F1" s="9" t="inlineStr">
+      <c r="G1" s="9" t="inlineStr">
         <is>
           <t>devise</t>
         </is>
       </c>
-      <c r="G1" s="9" t="inlineStr">
+      <c r="H1" s="9" t="inlineStr">
         <is>
           <t>portee_offre</t>
         </is>
       </c>
-      <c r="H1" s="9" t="inlineStr">
+      <c r="I1" s="9" t="inlineStr">
         <is>
           <t>oui_non</t>
         </is>
       </c>
-      <c r="I1" s="9" t="inlineStr">
+      <c r="J1" s="9" t="inlineStr">
         <is>
           <t>type_verdict</t>
         </is>
@@ -1131,45 +1823,50 @@
     <row r="2">
       <c r="A2" s="11" t="inlineStr">
         <is>
+          <t>evaluation</t>
+        </is>
+      </c>
+      <c r="B2" s="11" t="inlineStr">
+        <is>
           <t>futures</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
+      <c r="C2" s="11" t="inlineStr">
         <is>
           <t>evaluation</t>
         </is>
       </c>
-      <c r="C2" s="11" t="inlineStr">
+      <c r="D2" s="11" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="D2" s="11" t="inlineStr">
+      <c r="E2" s="11" t="inlineStr">
         <is>
           <t>evaluation</t>
         </is>
       </c>
-      <c r="E2" s="11" t="inlineStr">
+      <c r="F2" s="11" t="inlineStr">
         <is>
           <t>End of Day</t>
         </is>
       </c>
-      <c r="F2" s="11" t="inlineStr">
+      <c r="G2" s="11" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="G2" s="11" t="inlineStr">
+      <c r="H2" s="11" t="inlineStr">
         <is>
           <t>universelle_verifiee</t>
         </is>
       </c>
-      <c r="H2" s="11" t="inlineStr">
+      <c r="I2" s="11" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
       </c>
-      <c r="I2" s="11" t="inlineStr">
+      <c r="J2" s="11" t="inlineStr">
         <is>
           <t>verdict</t>
         </is>
@@ -1178,45 +1875,50 @@
     <row r="3">
       <c r="A3" s="11" t="inlineStr">
         <is>
+          <t>funded</t>
+        </is>
+      </c>
+      <c r="B3" s="11" t="inlineStr">
+        <is>
           <t>cfd</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
+      <c r="C3" s="11" t="inlineStr">
         <is>
           <t>instant</t>
         </is>
       </c>
-      <c r="C3" s="11" t="inlineStr">
+      <c r="D3" s="11" t="inlineStr">
         <is>
           <t>promotional</t>
         </is>
       </c>
-      <c r="D3" s="11" t="inlineStr">
+      <c r="E3" s="11" t="inlineStr">
         <is>
           <t>evaluation_2</t>
         </is>
       </c>
-      <c r="E3" s="11" t="inlineStr">
+      <c r="F3" s="11" t="inlineStr">
         <is>
           <t>Trailing Equity</t>
         </is>
       </c>
-      <c r="F3" s="11" t="inlineStr">
+      <c r="G3" s="11" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="G3" s="11" t="inlineStr">
+      <c r="H3" s="11" t="inlineStr">
         <is>
           <t>restreinte</t>
         </is>
       </c>
-      <c r="H3" s="11" t="inlineStr">
+      <c r="I3" s="11" t="inlineStr">
         <is>
           <t>non</t>
         </is>
       </c>
-      <c r="I3" s="11" t="inlineStr">
+      <c r="J3" s="11" t="inlineStr">
         <is>
           <t>pour_qui</t>
         </is>
@@ -1225,59 +1927,64 @@
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
         <is>
+          <t>payout</t>
+        </is>
+      </c>
+      <c r="B4" s="11" t="inlineStr">
+        <is>
           <t>stocks</t>
         </is>
       </c>
-      <c r="C4" s="11" t="inlineStr">
+      <c r="D4" s="11" t="inlineStr">
         <is>
           <t>retired</t>
         </is>
       </c>
-      <c r="D4" s="11" t="inlineStr">
+      <c r="E4" s="11" t="inlineStr">
         <is>
           <t>funded</t>
         </is>
       </c>
-      <c r="E4" s="11" t="inlineStr">
+      <c r="F4" s="11" t="inlineStr">
         <is>
           <t>Trailing Intraday</t>
         </is>
       </c>
-      <c r="F4" s="11" t="inlineStr">
+      <c r="G4" s="11" t="inlineStr">
         <is>
           <t>GBP</t>
         </is>
       </c>
-      <c r="G4" s="11" t="inlineStr">
+      <c r="H4" s="11" t="inlineStr">
         <is>
           <t>non_confirmee</t>
         </is>
       </c>
-      <c r="I4" s="11" t="inlineStr">
+      <c r="J4" s="11" t="inlineStr">
         <is>
           <t>pas_pour</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="11" t="inlineStr">
+      <c r="B5" s="11" t="inlineStr">
         <is>
           <t>crypto</t>
         </is>
       </c>
-      <c r="E5" s="11" t="inlineStr">
+      <c r="F5" s="11" t="inlineStr">
         <is>
           <t>Static</t>
         </is>
       </c>
-      <c r="I5" s="11" t="inlineStr">
+      <c r="J5" s="11" t="inlineStr">
         <is>
           <t>point_fort</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="I6" s="11" t="inlineStr">
+      <c r="J6" s="11" t="inlineStr">
         <is>
           <t>limite</t>
         </is>
@@ -2125,13 +2832,13 @@
   </sheetData>
   <dataValidations count="3">
     <dataValidation sqref="C3:C23" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valeur hors liste" error="Choisis une valeur dans la liste deroulante." type="list">
-      <formula1>=Listes!$A$2:$A$5</formula1>
+      <formula1>=Listes!$B$2:$B$5</formula1>
     </dataValidation>
     <dataValidation sqref="D3:D23" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valeur hors liste" error="Choisis une valeur dans la liste deroulante." type="list">
-      <formula1>=Listes!$B$2:$B$3</formula1>
+      <formula1>=Listes!$C$2:$C$3</formula1>
     </dataValidation>
     <dataValidation sqref="E3:E23" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valeur hors liste" error="Choisis une valeur dans la liste deroulante." type="list">
-      <formula1>=Listes!$C$2:$C$4</formula1>
+      <formula1>=Listes!$D$2:$D$4</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4846,10 +5553,10 @@
   </sheetData>
   <dataValidations count="2">
     <dataValidation sqref="D3:D153" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valeur hors liste" error="Choisis une valeur dans la liste deroulante." type="list">
-      <formula1>=Listes!$F$2:$F$4</formula1>
+      <formula1>=Listes!$G$2:$G$4</formula1>
     </dataValidation>
     <dataValidation sqref="F3:F153" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valeur hors liste" error="Choisis une valeur dans la liste deroulante." type="list">
-      <formula1>=Listes!$H$2:$H$3</formula1>
+      <formula1>=Listes!$I$2:$I$3</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -13003,10 +13710,10 @@
   </sheetData>
   <dataValidations count="2">
     <dataValidation sqref="D3:D404" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valeur hors liste" error="Choisis une valeur dans la liste deroulante." type="list">
-      <formula1>=Listes!$D$2:$D$4</formula1>
+      <formula1>=Listes!$E$2:$E$4</formula1>
     </dataValidation>
     <dataValidation sqref="G3:G404" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valeur hors liste" error="Choisis une valeur dans la liste deroulante." type="list">
-      <formula1>=Listes!$E$2:$E$5</formula1>
+      <formula1>=Listes!$F$2:$F$5</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -13193,10 +13900,10 @@
   </sheetData>
   <dataValidations count="2">
     <dataValidation sqref="B4" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valeur hors liste" error="Choisis une valeur dans la liste deroulante." type="list">
-      <formula1>=Listes!$G$2:$G$4</formula1>
+      <formula1>=Listes!$H$2:$H$4</formula1>
     </dataValidation>
     <dataValidation sqref="B5" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valeur hors liste" error="Choisis une valeur dans la liste deroulante." type="list">
-      <formula1>=Listes!$H$2:$H$3</formula1>
+      <formula1>=Listes!$I$2:$I$3</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -13317,30 +14024,36 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="006B7280"/>
+    <tabColor rgb="004B5563"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C37"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="96" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="90" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="14" t="inlineStr">
         <is>
-          <t>type</t>
+          <t>ordre</t>
         </is>
       </c>
       <c r="B1" s="14" t="inlineStr">
         <is>
-          <t>ordre</t>
+          <t>etape</t>
         </is>
       </c>
       <c r="C1" s="14" t="inlineStr">
+        <is>
+          <t>titre</t>
+        </is>
+      </c>
+      <c r="D1" s="14" t="inlineStr">
         <is>
           <t>texte</t>
         </is>
@@ -13349,409 +14062,161 @@
     <row r="2" ht="58" customHeight="1">
       <c r="A2" s="21" t="inlineStr">
         <is>
-          <t>verdict = « Our verdict » · pour_qui = liste ✓ · pas_pour = « Consider another firm if… » · point_fort = « Strengths » · limite = « Things to know »</t>
+          <t>1, 2, 3 : l'ordre des etapes, de gauche a droite.</t>
         </is>
       </c>
       <c r="B2" s="21" t="inlineStr">
         <is>
-          <t>1, 2, 3 dans chaque type. Le gabarit en montre 3.</t>
+          <t>evaluation, funded ou payout. Sert le petit titre au-dessus de l'etape.</t>
         </is>
       </c>
       <c r="C2" s="21" t="inlineStr">
         <is>
-          <t>Conclusion independante, sans superlatif marketing.</t>
+          <t>Le titre de l'etape, en quelques mots.</t>
+        </is>
+      </c>
+      <c r="D2" s="21" t="inlineStr">
+        <is>
+          <t>Ce qui se passe a cette etape, au niveau de la firme. Les differences entre programmes restent dans « Which program fits you? ».</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="16" t="inlineStr">
-        <is>
-          <t>verdict</t>
-        </is>
-      </c>
-      <c r="B3" s="19" t="n">
+      <c r="A3" s="19" t="n">
         <v>1</v>
       </c>
+      <c r="B3" s="16" t="inlineStr">
+        <is>
+          <t>evaluation</t>
+        </is>
+      </c>
       <c r="C3" s="16" t="inlineStr">
         <is>
-          <t>FuturesElite bets on generous terms once you are funded: up to a 90% split, daily payouts, and no funded consistency rule on Elite and Nitro. In exchange, the firm is young and is a proprietary trading company rather than a regulated broker.</t>
+          <t>Pass the evaluation</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>One phase on Elite, Nitro and Prime: reach the profit objective without breaching the maximum loss. There is no deadline to pass. Minimum trading days differ by programme, and Instant has no evaluation at all.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="16" t="inlineStr">
-        <is>
-          <t>pour_qui</t>
-        </is>
-      </c>
-      <c r="B4" s="19" t="n">
-        <v>1</v>
+      <c r="A4" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" s="16" t="inlineStr">
+        <is>
+          <t>funded</t>
+        </is>
       </c>
       <c r="C4" s="16" t="inlineStr">
         <is>
-          <t>A high split and frequent payouts, with no waiting period</t>
+          <t>Get the funded account</t>
+        </is>
+      </c>
+      <c r="D4" s="16" t="inlineStr">
+        <is>
+          <t>The simulated funded account opens with no activation fee. Drawdown type and contract scaling change with the programme, so the rules table above is the one that applies.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="16" t="inlineStr">
-        <is>
-          <t>pour_qui</t>
-        </is>
-      </c>
-      <c r="B5" s="19" t="n">
-        <v>2</v>
+      <c r="A5" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" s="16" t="inlineStr">
+        <is>
+          <t>payout</t>
+        </is>
       </c>
       <c r="C5" s="16" t="inlineStr">
         <is>
-          <t>Elite or Nitro evaluations without a daily loss limit, which leaves room to breathe</t>
+          <t>Request your first payout</t>
+        </is>
+      </c>
+      <c r="D5" s="16" t="inlineStr">
+        <is>
+          <t>Requests can be made every day and are reviewed in under 24 hours on average, then paid through Rise once KYC is done with Veriff. Each request is capped by account size, and minimum trading days apply first.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="16" t="inlineStr">
-        <is>
-          <t>pour_qui</t>
-        </is>
-      </c>
-      <c r="B6" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="C6" s="16" t="inlineStr">
-        <is>
-          <t>A funded account that opens with no activation fee</t>
-        </is>
-      </c>
+      <c r="A6" s="19" t="n"/>
+      <c r="B6" s="16" t="n"/>
+      <c r="C6" s="16" t="n"/>
+      <c r="D6" s="16" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="16" t="inlineStr">
-        <is>
-          <t>pour_qui</t>
-        </is>
-      </c>
-      <c r="B7" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>The option to stack up to ten accounts in parallel</t>
-        </is>
-      </c>
+      <c r="A7" s="19" t="n"/>
+      <c r="B7" s="16" t="n"/>
+      <c r="C7" s="16" t="n"/>
+      <c r="D7" s="16" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="16" t="inlineStr">
-        <is>
-          <t>pas_pour</t>
-        </is>
-      </c>
-      <c r="B8" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="C8" s="16" t="inlineStr">
-        <is>
-          <t>You want a regulated broker: Quantum SRL holds no financial regulator licence.</t>
-        </is>
-      </c>
+      <c r="A8" s="19" t="n"/>
+      <c r="B8" s="16" t="n"/>
+      <c r="C8" s="16" t="n"/>
+      <c r="D8" s="16" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="16" t="inlineStr">
-        <is>
-          <t>pas_pour</t>
-        </is>
-      </c>
-      <c r="B9" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="C9" s="16" t="inlineStr">
-        <is>
-          <t>You want real capital: every account is simulated, and performance stays hypothetical.</t>
-        </is>
-      </c>
+      <c r="A9" s="19" t="n"/>
+      <c r="B9" s="16" t="n"/>
+      <c r="C9" s="16" t="n"/>
+      <c r="D9" s="16" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="16" t="inlineStr">
-        <is>
-          <t>pas_pour</t>
-        </is>
-      </c>
-      <c r="B10" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="C10" s="16" t="inlineStr">
-        <is>
-          <t>You run fully automated systems: AI and bots are prohibited.</t>
-        </is>
-      </c>
+      <c r="A10" s="19" t="n"/>
+      <c r="B10" s="16" t="n"/>
+      <c r="C10" s="16" t="n"/>
+      <c r="D10" s="16" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="16" t="inlineStr">
-        <is>
-          <t>pas_pour</t>
-        </is>
-      </c>
-      <c r="B11" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="C11" s="16" t="inlineStr">
-        <is>
-          <t>You want to withdraw a whole balance at once: each request is capped by account size.</t>
-        </is>
-      </c>
+      <c r="A11" s="19" t="n"/>
+      <c r="B11" s="16" t="n"/>
+      <c r="C11" s="16" t="n"/>
+      <c r="D11" s="16" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="16" t="inlineStr">
-        <is>
-          <t>pas_pour</t>
-        </is>
-      </c>
-      <c r="B12" s="19" t="n">
-        <v>5</v>
-      </c>
-      <c r="C12" s="16" t="inlineStr">
-        <is>
-          <t>You need a guaranteed route to live trading: it is a risk-team decision, not an entitlement.</t>
-        </is>
-      </c>
+      <c r="A12" s="19" t="n"/>
+      <c r="B12" s="16" t="n"/>
+      <c r="C12" s="16" t="n"/>
+      <c r="D12" s="16" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="16" t="inlineStr">
-        <is>
-          <t>point_fort</t>
-        </is>
-      </c>
-      <c r="B13" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="C13" s="16" t="inlineStr">
-        <is>
-          <t>90% profit split on Elite, Nitro and Prime; 80% on Instant</t>
-        </is>
-      </c>
+      <c r="A13" s="19" t="n"/>
+      <c r="B13" s="16" t="n"/>
+      <c r="C13" s="16" t="n"/>
+      <c r="D13" s="16" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="16" t="inlineStr">
-        <is>
-          <t>point_fort</t>
-        </is>
-      </c>
-      <c r="B14" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="C14" s="16" t="inlineStr">
-        <is>
-          <t>Drawdown type differs by program and phase — see the rules table</t>
-        </is>
-      </c>
+      <c r="A14" s="19" t="n"/>
+      <c r="B14" s="16" t="n"/>
+      <c r="C14" s="16" t="n"/>
+      <c r="D14" s="16" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="16" t="inlineStr">
-        <is>
-          <t>point_fort</t>
-        </is>
-      </c>
-      <c r="B15" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="C15" s="16" t="inlineStr">
-        <is>
-          <t>No daily loss limit on Elite, Nitro and Instant — Prime has one in both phases</t>
-        </is>
-      </c>
+      <c r="A15" s="19" t="n"/>
+      <c r="B15" s="16" t="n"/>
+      <c r="C15" s="16" t="n"/>
+      <c r="D15" s="16" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="16" t="inlineStr">
-        <is>
-          <t>point_fort</t>
-        </is>
-      </c>
-      <c r="B16" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="C16" s="16" t="inlineStr">
-        <is>
-          <t>No funded consistency rule on Elite and Nitro</t>
-        </is>
-      </c>
+      <c r="A16" s="19" t="n"/>
+      <c r="B16" s="16" t="n"/>
+      <c r="C16" s="16" t="n"/>
+      <c r="D16" s="16" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="16" t="inlineStr">
-        <is>
-          <t>point_fort</t>
-        </is>
-      </c>
-      <c r="B17" s="19" t="n">
-        <v>5</v>
-      </c>
-      <c r="C17" s="16" t="inlineStr">
-        <is>
-          <t>No activation fee to unlock the funded account</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="16" t="inlineStr">
-        <is>
-          <t>point_fort</t>
-        </is>
-      </c>
-      <c r="B18" s="19" t="n">
-        <v>6</v>
-      </c>
-      <c r="C18" s="16" t="inlineStr">
-        <is>
-          <t>Payouts available every day once funded</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="16" t="inlineStr">
-        <is>
-          <t>point_fort</t>
-        </is>
-      </c>
-      <c r="B19" s="19" t="n">
-        <v>7</v>
-      </c>
-      <c r="C19" s="16" t="inlineStr">
-        <is>
-          <t>Bundle discounts: the fifth account is free</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="16" t="inlineStr">
-        <is>
-          <t>limite</t>
-        </is>
-      </c>
-      <c r="B20" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="C20" s="16" t="inlineStr">
-        <is>
-          <t>No financial regulator licence</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="16" t="inlineStr">
-        <is>
-          <t>limite</t>
-        </is>
-      </c>
-      <c r="B21" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="C21" s="16" t="inlineStr">
-        <is>
-          <t>Demo accounts, hypothetical performance</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="16" t="inlineStr">
-        <is>
-          <t>limite</t>
-        </is>
-      </c>
-      <c r="B22" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="C22" s="16" t="inlineStr">
-        <is>
-          <t>Minimum days differ by program; Elite needs 6 profitable days above a size-based threshold before a payout</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="16" t="inlineStr">
-        <is>
-          <t>limite</t>
-        </is>
-      </c>
-      <c r="B23" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="C23" s="16" t="inlineStr">
-        <is>
-          <t>Per-request payout cap, from $1,000 to $3,000 by account size</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="16" t="n"/>
-      <c r="B24" s="19" t="n"/>
-      <c r="C24" s="16" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="16" t="n"/>
-      <c r="B25" s="19" t="n"/>
-      <c r="C25" s="16" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="16" t="n"/>
-      <c r="B26" s="19" t="n"/>
-      <c r="C26" s="16" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="16" t="n"/>
-      <c r="B27" s="19" t="n"/>
-      <c r="C27" s="16" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="16" t="n"/>
-      <c r="B28" s="19" t="n"/>
-      <c r="C28" s="16" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="16" t="n"/>
-      <c r="B29" s="19" t="n"/>
-      <c r="C29" s="16" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="16" t="n"/>
-      <c r="B30" s="19" t="n"/>
-      <c r="C30" s="16" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="16" t="n"/>
-      <c r="B31" s="19" t="n"/>
-      <c r="C31" s="16" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="16" t="n"/>
-      <c r="B32" s="19" t="n"/>
-      <c r="C32" s="16" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="16" t="n"/>
-      <c r="B33" s="19" t="n"/>
-      <c r="C33" s="16" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="16" t="n"/>
-      <c r="B34" s="19" t="n"/>
-      <c r="C34" s="16" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="16" t="n"/>
-      <c r="B35" s="19" t="n"/>
-      <c r="C35" s="16" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="16" t="n"/>
-      <c r="B36" s="19" t="n"/>
-      <c r="C36" s="16" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="16" t="n"/>
-      <c r="B37" s="19" t="n"/>
-      <c r="C37" s="16" t="n"/>
+      <c r="A17" s="19" t="n"/>
+      <c r="B17" s="16" t="n"/>
+      <c r="C17" s="16" t="n"/>
+      <c r="D17" s="16" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="A3:A37" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valeur hors liste" error="Choisis une valeur dans la liste deroulante." type="list">
-      <formula1>=Listes!$I$2:$I$6</formula1>
+    <dataValidation sqref="B3:B17" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valeur hors liste" error="Choisis une valeur dans la liste deroulante." type="list">
+      <formula1>=Listes!$A$2:$A$4</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -13762,16 +14227,17 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="006B7280"/>
+    <tabColor rgb="004B5563"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="80" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="80" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -13782,29 +14248,39 @@
       </c>
       <c r="B1" s="14" t="inlineStr">
         <is>
-          <t>question</t>
+          <t>libelle</t>
         </is>
       </c>
       <c r="C1" s="14" t="inlineStr">
         <is>
-          <t>reponse</t>
+          <t>montant</t>
+        </is>
+      </c>
+      <c r="D1" s="14" t="inlineStr">
+        <is>
+          <t>note</t>
         </is>
       </c>
     </row>
     <row r="2" ht="58" customHeight="1">
       <c r="A2" s="21" t="inlineStr">
         <is>
-          <t>Ordre d'affichage.</t>
+          <t>1, 2, 3 : l'ordre des lignes.</t>
         </is>
       </c>
       <c r="B2" s="21" t="inlineStr">
         <is>
-          <t>Les 5 questions du gabarit sont pre-remplies ; [Firm] sera remplace par le nom. Tu peux en ajouter.</t>
+          <t>Le nom du frais, tel qu'il s'affiche.</t>
         </is>
       </c>
       <c r="C2" s="21" t="inlineStr">
         <is>
-          <t>Vide : la page recompose la reponse depuis les autres onglets (programmes, prix, partage, retraits, offre).</t>
+          <t>Texte libre : « $95 – $569 », « None », « Per contract ». Vide : la ligne affiche « — ».</t>
+        </is>
+      </c>
+      <c r="D2" s="21" t="inlineStr">
+        <is>
+          <t>Quand il se paie, et a quelle condition. Vide : rien sous le montant.</t>
         </is>
       </c>
     </row>
@@ -13814,10 +14290,19 @@
       </c>
       <c r="B3" s="16" t="inlineStr">
         <is>
-          <t>Is [Firm] suitable for beginners?</t>
-        </is>
-      </c>
-      <c r="C3" s="16" t="n"/>
+          <t>Account purchase</t>
+        </is>
+      </c>
+      <c r="C3" s="16" t="inlineStr">
+        <is>
+          <t>$95 – $569</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>One-time fee per account, no monthly subscription. The price depends on the programme and the account size.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="19" t="n">
@@ -13825,10 +14310,19 @@
       </c>
       <c r="B4" s="16" t="inlineStr">
         <is>
-          <t>How much does [Firm] cost?</t>
-        </is>
-      </c>
-      <c r="C4" s="16" t="n"/>
+          <t>Reset after a breach</t>
+        </is>
+      </c>
+      <c r="C4" s="16" t="inlineStr">
+        <is>
+          <t>$79 – $229</t>
+        </is>
+      </c>
+      <c r="D4" s="16" t="inlineStr">
+        <is>
+          <t>Optional, on the evaluation programmes only. Buying a new account instead is always possible.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="19" t="n">
@@ -13836,10 +14330,19 @@
       </c>
       <c r="B5" s="16" t="inlineStr">
         <is>
-          <t>What profit split does [Firm] offer?</t>
-        </is>
-      </c>
-      <c r="C5" s="16" t="n"/>
+          <t>Funded account activation</t>
+        </is>
+      </c>
+      <c r="C5" s="16" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D5" s="16" t="inlineStr">
+        <is>
+          <t>No activation fee once the evaluation is passed.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="19" t="n">
@@ -13847,10 +14350,19 @@
       </c>
       <c r="B6" s="16" t="inlineStr">
         <is>
-          <t>How do payouts work?</t>
-        </is>
-      </c>
-      <c r="C6" s="16" t="n"/>
+          <t>Trading costs</t>
+        </is>
+      </c>
+      <c r="C6" s="16" t="inlineStr">
+        <is>
+          <t>Per contract</t>
+        </is>
+      </c>
+      <c r="D6" s="16" t="inlineStr">
+        <is>
+          <t>Commissions and exchange fees are charged per instrument on each executed trade.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="19" t="n">
@@ -13858,85 +14370,91 @@
       </c>
       <c r="B7" s="16" t="inlineStr">
         <is>
-          <t>Does the promotional code apply to every account?</t>
-        </is>
-      </c>
-      <c r="C7" s="16" t="n"/>
+          <t>First payout</t>
+        </is>
+      </c>
+      <c r="C7" s="16" t="inlineStr">
+        <is>
+          <t>$500 minimum on Elite</t>
+        </is>
+      </c>
+      <c r="D7" s="16" t="inlineStr">
+        <is>
+          <t>Requests are capped from $1,000 to $3,500 by account size. Elite asks for 6 trading days first.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="19" t="n"/>
       <c r="B8" s="16" t="n"/>
       <c r="C8" s="16" t="n"/>
+      <c r="D8" s="16" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="19" t="n"/>
       <c r="B9" s="16" t="n"/>
       <c r="C9" s="16" t="n"/>
+      <c r="D9" s="16" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="19" t="n"/>
       <c r="B10" s="16" t="n"/>
       <c r="C10" s="16" t="n"/>
+      <c r="D10" s="16" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="19" t="n"/>
       <c r="B11" s="16" t="n"/>
       <c r="C11" s="16" t="n"/>
+      <c r="D11" s="16" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="19" t="n"/>
       <c r="B12" s="16" t="n"/>
       <c r="C12" s="16" t="n"/>
+      <c r="D12" s="16" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="19" t="n"/>
       <c r="B13" s="16" t="n"/>
       <c r="C13" s="16" t="n"/>
+      <c r="D13" s="16" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="19" t="n"/>
       <c r="B14" s="16" t="n"/>
       <c r="C14" s="16" t="n"/>
+      <c r="D14" s="16" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="19" t="n"/>
       <c r="B15" s="16" t="n"/>
       <c r="C15" s="16" t="n"/>
+      <c r="D15" s="16" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="19" t="n"/>
       <c r="B16" s="16" t="n"/>
       <c r="C16" s="16" t="n"/>
+      <c r="D16" s="16" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="19" t="n"/>
       <c r="B17" s="16" t="n"/>
       <c r="C17" s="16" t="n"/>
+      <c r="D17" s="16" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="19" t="n"/>
       <c r="B18" s="16" t="n"/>
       <c r="C18" s="16" t="n"/>
+      <c r="D18" s="16" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="19" t="n"/>
       <c r="B19" s="16" t="n"/>
       <c r="C19" s="16" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="19" t="n"/>
-      <c r="B20" s="16" t="n"/>
-      <c r="C20" s="16" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="19" t="n"/>
-      <c r="B21" s="16" t="n"/>
-      <c r="C21" s="16" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="19" t="n"/>
-      <c r="B22" s="16" t="n"/>
-      <c r="C22" s="16" t="n"/>
+      <c r="D19" s="16" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
